--- a/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,289 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>146800</v>
+        <v>140300</v>
       </c>
       <c r="E8" s="3">
-        <v>143700</v>
+        <v>134600</v>
       </c>
       <c r="F8" s="3">
-        <v>117100</v>
+        <v>135800</v>
       </c>
       <c r="G8" s="3">
-        <v>155600</v>
+        <v>102900</v>
       </c>
       <c r="H8" s="3">
-        <v>179300</v>
+        <v>146900</v>
       </c>
       <c r="I8" s="3">
-        <v>258300</v>
+        <v>157200</v>
       </c>
       <c r="J8" s="3">
+        <v>228200</v>
+      </c>
+      <c r="K8" s="3">
         <v>314000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>287400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>210400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>187300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>116200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>84400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>62900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>68000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>61100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>47900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>28600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E9" s="3">
         <v>36900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>36800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>40600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>43500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>45000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>51100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>48400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>41000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>35000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>24200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>109900</v>
+        <v>104200</v>
       </c>
       <c r="E10" s="3">
-        <v>106900</v>
+        <v>97700</v>
       </c>
       <c r="F10" s="3">
-        <v>76500</v>
+        <v>99000</v>
       </c>
       <c r="G10" s="3">
-        <v>112100</v>
+        <v>62300</v>
       </c>
       <c r="H10" s="3">
-        <v>134300</v>
+        <v>103400</v>
       </c>
       <c r="I10" s="3">
-        <v>207200</v>
+        <v>112200</v>
       </c>
       <c r="J10" s="3">
+        <v>177100</v>
+      </c>
+      <c r="K10" s="3">
         <v>265600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>246400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>175400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>163100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>98800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>71600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>53500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>59200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>52700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>41200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>57200</v>
+      </c>
+      <c r="E12" s="3">
         <v>54900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>58000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>110100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>64000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>66200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>57000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>50000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>46500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>37100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>31400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>19000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1085,8 +1101,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1147,8 +1166,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1209,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>190600</v>
+        <v>187800</v>
       </c>
       <c r="E17" s="3">
-        <v>177000</v>
+        <v>178400</v>
       </c>
       <c r="F17" s="3">
-        <v>249000</v>
+        <v>169100</v>
       </c>
       <c r="G17" s="3">
-        <v>214100</v>
+        <v>234800</v>
       </c>
       <c r="H17" s="3">
-        <v>237400</v>
+        <v>205400</v>
       </c>
       <c r="I17" s="3">
-        <v>290500</v>
+        <v>215300</v>
       </c>
       <c r="J17" s="3">
+        <v>260300</v>
+      </c>
+      <c r="K17" s="3">
         <v>279100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>227000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>181800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>151000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>100600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>74000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>53200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>63400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>59100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>47500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>34100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-43800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-33300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-131900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-58500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-58100</v>
       </c>
-      <c r="I18" s="3">
-        <v>-32200</v>
-      </c>
       <c r="J18" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="K18" s="3">
         <v>34900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>60400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>28600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>36300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-15400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1378,132 +1410,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E20" s="3">
         <v>3500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="I20" s="3">
-        <v>2300</v>
-      </c>
       <c r="J20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-700</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-5300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>9300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-35400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-23700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-122800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-52100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-52500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>35500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>61800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>30000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>38300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T21" s="3">
         <v>5700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1564,75 +1603,81 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-40300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-28100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-129200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-55700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-56200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-29800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>32700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>59300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>27800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>36300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1641,11 +1686,11 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-500</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -1653,23 +1698,23 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1677,19 +1722,22 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-40300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-129300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-55300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-56200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-29900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>32700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>58900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>29100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>37300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-40300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-129300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-55300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-56200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-29900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>32700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>58900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>29100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>37300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>9700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="I32" s="3">
-        <v>-2300</v>
-      </c>
       <c r="J32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="K32" s="3">
         <v>2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>700</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>5300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-9300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-40300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-129300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-55300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-56200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-29900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>32700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>58900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>29100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>37300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-40300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-129300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-55300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-56200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-29900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>32700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>58900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>29100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>37300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,53 +2570,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>368400</v>
+      </c>
+      <c r="E41" s="3">
         <v>516600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>443700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>386900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>422400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>684000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>790400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>757800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>986600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1041500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>506300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>257000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>250800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>53200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2547,8 +2633,11 @@
       <c r="V41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2609,53 +2698,56 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E43" s="3">
         <v>41200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>46100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>42900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>46700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>49900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>48600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>55500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>30000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>31700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2671,8 +2763,11 @@
       <c r="V43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2733,8 +2828,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2795,8 +2893,11 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2857,53 +2958,56 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1240600</v>
+      </c>
+      <c r="E47" s="3">
         <v>1046500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>916100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1063100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1094300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>782000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>704600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>673300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>319200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>192500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>110800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>82000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>104400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>151300</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>16</v>
       </c>
@@ -2919,53 +3023,56 @@
       <c r="V47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>97300</v>
+      </c>
+      <c r="E48" s="3">
         <v>125300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>127400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>130400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>130500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>128500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>126400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>123000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>120400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>88900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>29800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>28300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>23000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2981,44 +3088,47 @@
       <c r="V48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>78400</v>
+      </c>
+      <c r="E49" s="3">
         <v>79500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>80600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>81600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>82700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>83800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>84800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>85900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>87000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>87800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>89000</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3034,8 +3144,8 @@
       <c r="S49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3043,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,53 +3283,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>117400</v>
+      </c>
+      <c r="E52" s="3">
         <v>119500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>83800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>86900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>126800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>169500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>146400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>283700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>234600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>148200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>126200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>93300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>66500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>60500</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3229,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,53 +3413,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2017100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2001800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1763700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1821700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1936100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1915300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1917000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1987600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1820500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1606100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>904600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>488600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>477300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>309800</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3353,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,53 +3530,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E57" s="3">
         <v>58600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>51000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>47600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>109500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>104800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>127700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>150100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>114200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>93700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>94300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>64600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>59300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>45200</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3463,8 +3593,11 @@
       <c r="V57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3499,16 +3632,16 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>20500</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>16</v>
+      <c r="P58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>16</v>
@@ -3519,59 +3652,62 @@
       <c r="T58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E59" s="3">
         <v>288100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>133600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>131500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>146100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>149200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>154700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>169800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>185900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>128700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>67000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>44700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>44200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>29900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3587,8 +3723,11 @@
       <c r="V59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3649,53 +3788,56 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1040400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1003400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>930700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1000900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>986400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>918900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>856600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>769200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>695400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>649200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>62600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>100600</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3711,8 +3853,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3773,8 +3918,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,53 +4113,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1381800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1361000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1125600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1194500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1263600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1196700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1159900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1111100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1013400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>887000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>188500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>168000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>177000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>194600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4021,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4211,11 +4378,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>162500</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,53 +4463,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-282600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-240200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-199900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-171700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-42400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>69000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>98900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>66200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-21800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-59100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-69200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-70200</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4355,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,53 +4723,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>635300</v>
+      </c>
+      <c r="E76" s="3">
         <v>640800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>638100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>627200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>672400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>718600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>757100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>876500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>807100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>719100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>716100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>320600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>300300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-47300</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4603,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-40300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-129300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-55300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-56200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-29900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>32700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>58900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>29100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>37300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,50 +5015,51 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E83" s="3">
         <v>4900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>3700</v>
       </c>
       <c r="H83" s="3">
         <v>3700</v>
       </c>
       <c r="I83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J83" s="3">
         <v>3400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>600</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>16</v>
       </c>
@@ -4880,8 +5078,11 @@
       <c r="V83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,50 +5403,53 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-143700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-103400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>162400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-75700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-252900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-101400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-53600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-266800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>43600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>92800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>43100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>68500</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5252,8 +5468,11 @@
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,50 +5495,51 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>16</v>
       </c>
@@ -5338,8 +5558,11 @@
       <c r="V91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,50 +5688,53 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-24200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-38500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-25900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-85100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-24200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>5200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-84400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-40600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>8800</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5524,8 +5753,11 @@
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,50 +6038,53 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E100" s="3">
         <v>232800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-65900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>21000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>40500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>41100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-34700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>83100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>50400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>595000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>229300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-19300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>123400</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>16</v>
       </c>
@@ -5858,8 +6103,11 @@
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5920,50 +6168,53 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-147200</v>
+      </c>
+      <c r="E102" s="3">
         <v>105100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>58000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-80600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-297500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-84500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-98300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-178500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>19500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>554200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>281500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>24700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>200700</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>16</v>
       </c>
@@ -5980,6 +6231,9 @@
         <v>16</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
@@ -656,301 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>127800</v>
+      </c>
+      <c r="E8" s="3">
         <v>140300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>134600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>135800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>102900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>146900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>157200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>228200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>314000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>287400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>210400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>187300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>116200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>84400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>62900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>68000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>61100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>47900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>28600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E9" s="3">
         <v>36100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>36900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>36800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>40600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>43500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>45000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>51100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>48400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>41000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>35000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>88400</v>
+      </c>
+      <c r="E10" s="3">
         <v>104200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>97700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>99000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>62300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>103400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>112200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>177100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>265600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>246400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>175400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>163100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>98800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>71600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>53500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>59200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>52700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>41200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>23200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E12" s="3">
         <v>57200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>54900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>58000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>110100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>64000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>66200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>57000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>50000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>46500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>37100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>31400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>19000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1169,8 +1189,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>195300</v>
+      </c>
+      <c r="E17" s="3">
         <v>187800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>178400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>169100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>234800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>205400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>215300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>260300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>279100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>227000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>181800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>151000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>100600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>74000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>53200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>28700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>63400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>59100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>47500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>34100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-67500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-47500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-43800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-33300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-131900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-58500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-58100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-32100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>34900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>60400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>28600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>36300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>15600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-15400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1411,138 +1444,145 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E20" s="3">
         <v>5200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-5300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>9300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-33200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-35400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-23700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-122800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-52100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-52500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-26500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>35500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>61800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>30000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>38300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U21" s="3">
         <v>5700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>100</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1606,82 +1646,88 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-42300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-40300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-28100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-129200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-55700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-56200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-29800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>32700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>59300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>27800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>36300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>10300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>9700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -1689,11 +1735,11 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-500</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1701,23 +1747,23 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1725,19 +1771,22 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-42400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-40300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-28200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-129300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-55300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-56200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-29900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>32700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>58900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>29100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>37300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-42400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-40300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-28200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-129300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-55300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-56200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-29900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>32700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>58900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>29100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>37300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>5300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-9300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-42400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-40300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-28200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-129300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-55300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-56200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-29900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>32700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>58900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>29100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>37300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-42400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-40300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-28200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-129300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-55300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-56200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-29900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>32700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>58900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>29100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>37300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,56 +2657,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300500</v>
+      </c>
+      <c r="E41" s="3">
         <v>368400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>516600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>443700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>386900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>422400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>684000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>790400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>757800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>986600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1041500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>506300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>257000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>250800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>53200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2636,8 +2723,11 @@
       <c r="W41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,56 +2791,59 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E43" s="3">
         <v>40500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>41200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>46100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>42900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>46700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>49900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>46100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>48600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>55500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>30000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>31700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9100</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2766,8 +2859,11 @@
       <c r="W43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2831,8 +2927,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2896,8 +2995,11 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2961,56 +3063,59 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1162200</v>
+      </c>
+      <c r="E47" s="3">
         <v>1240600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1046500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>916100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1063100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1094300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>782000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>704600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>673300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>319200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>192500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>110800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>82000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>104400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>151300</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3026,56 +3131,59 @@
       <c r="W47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>92500</v>
+      </c>
+      <c r="E48" s="3">
         <v>97300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>125300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>127400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>130400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>130500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>128500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>126400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>123000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>120400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>88900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>29800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>23000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3091,47 +3199,50 @@
       <c r="W48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>77300</v>
+      </c>
+      <c r="E49" s="3">
         <v>78400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>79500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>80600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>81600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>82700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>83800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>84800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>85900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>87000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>87800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>89000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3147,8 +3258,8 @@
       <c r="T49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,56 +3403,59 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>161600</v>
+      </c>
+      <c r="E52" s="3">
         <v>117400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>119500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>83800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>86900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>126800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>169500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>146400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>283700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>234600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>148200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>126200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>93300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>66500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>60500</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,56 +3539,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1927700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2017100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2001800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1763700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1821700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1936100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1915300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1917000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1987600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1820500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1606100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>904600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>488600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>477300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>309800</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3481,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,56 +3661,57 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E57" s="3">
         <v>66200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>58600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>51000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>47600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>109500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>104800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>127700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>150100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>114200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>93700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>94300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>64600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>59300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>45200</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3596,8 +3727,11 @@
       <c r="W57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3635,16 +3769,16 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>20500</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>16</v>
+      <c r="Q58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>16</v>
@@ -3655,62 +3789,65 @@
       <c r="U58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>223900</v>
+      </c>
+      <c r="E59" s="3">
         <v>262000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>288100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>133600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>131500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>146100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>149200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>154700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>169800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>185900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>128700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>67000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>44700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>44200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>29900</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3726,8 +3863,11 @@
       <c r="W59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3791,56 +3931,59 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1005300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1040400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1003400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>930700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1000900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>986400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>918900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>856600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>769200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>695400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>649200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>62600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>100600</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3856,8 +3999,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,56 +4271,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1314900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1381800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1361000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1125600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1194500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1263600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1196700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1159900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1111100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1013400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>887000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>188500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>168000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>177000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>194600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4381,11 +4549,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>162500</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,56 +4637,59 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-347200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-282600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-240200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-199900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-171700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-42400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>69000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>98900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>66200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-21800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-59100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-70200</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,56 +4909,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>612800</v>
+      </c>
+      <c r="E76" s="3">
         <v>635300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>640800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>638100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>627200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>672400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>718600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>757100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>876500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>807100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>719100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>716100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>320600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>300300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-47300</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4791,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-42400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-40300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-28200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-129300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-55300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-56200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-29900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>32700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>58900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>29100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>37300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,53 +5214,54 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E83" s="3">
         <v>9100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>3700</v>
       </c>
       <c r="I83" s="3">
         <v>3700</v>
       </c>
       <c r="J83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K83" s="3">
         <v>3400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>600</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,53 +5620,56 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>52600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-143700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-103400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>162400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-75700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-252900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-101400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-53600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-266800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>43600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>92800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>43100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>68500</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5471,8 +5688,11 @@
       <c r="W89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,8 +5716,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5505,44 +5726,44 @@
         <v>-1700</v>
       </c>
       <c r="E91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>16</v>
       </c>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,53 +5918,56 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-29900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-24200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-38500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-85100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-24200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>5200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-84400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-40600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>8800</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5756,8 +5986,11 @@
       <c r="W94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,53 +6284,56 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="E100" s="3">
         <v>26400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>232800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-65900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>21000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>40500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>41100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-34700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>83100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>50400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>595000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>229300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-19300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>123400</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6106,8 +6352,11 @@
       <c r="W100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6171,53 +6420,56 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-147200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>105100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>58000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-80600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-297500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-84500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-98300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-178500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>19500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>554200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>281500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>24700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>200700</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6234,6 +6486,9 @@
         <v>16</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
@@ -656,314 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>127600</v>
+      </c>
+      <c r="E8" s="3">
         <v>127800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>140300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>134600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>135800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>102900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>146900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>157200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>228200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>314000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>287400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>210400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>187300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>116200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>84400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>62900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>68000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>61100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>47900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>28600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E9" s="3">
         <v>39400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>36100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>36900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>36800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>40600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>43500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>45000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>51100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>48400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>41000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>35000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>17400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E10" s="3">
         <v>88400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>104200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>97700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>99000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>62300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>103400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>112200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>177100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>265600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>246400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>175400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>163100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>98800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>71600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>53500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>59200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>52700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>41200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>23200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,76 +1001,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>58500</v>
+      </c>
+      <c r="E12" s="3">
         <v>63100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>57200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>54900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>58000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>110100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>64000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>66200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>57000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>50000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>46500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>37100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>31400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>19000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1124,8 +1141,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1192,8 +1212,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>183100</v>
+      </c>
+      <c r="E17" s="3">
         <v>195300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>187800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>178400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>169100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>234800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>205400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>215300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>260300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>279100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>227000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>181800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>151000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>100600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>74000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>53200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>28700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>63400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>59100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>47500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>34100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-67500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-47500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-43800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-33300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-131900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-58500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-58100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-32100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>34900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>60400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>28600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>36300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-15400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1445,144 +1478,151 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>2900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-700</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>9300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-59000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-33200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-35400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-23700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-122800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-52100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-52500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>35500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>61800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>30000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>38300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V21" s="3">
         <v>5700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1649,76 +1689,82 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-54500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-64600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-42300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-40300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-28100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-129200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-55700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-56200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-29800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>32700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>59300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>27800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>36300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1726,11 +1772,11 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -1738,11 +1784,11 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-500</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1750,23 +1796,23 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -1774,19 +1820,22 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-54500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-64600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-42400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-40300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-28200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-129300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-55300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-56200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-29900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>32700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>58900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>29100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>37300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-54500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-64600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-42400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-40300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-129300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-55300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-56200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-29900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>32700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>58900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>29100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>37300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>9700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>700</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>5300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-9300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-54500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-64600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-42400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-40300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-129300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-55300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-56200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>32700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>58900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>29100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>37300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>9700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-54500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-64600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-42400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-40300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-129300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-55300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-56200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>32700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>58900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>29100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>37300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>9700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,59 +2744,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>374800</v>
+      </c>
+      <c r="E41" s="3">
         <v>300500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>368400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>516600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>443700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>386900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>422400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>684000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>790400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>757800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>986600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1041500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>506300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>257000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>250800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>53200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2726,8 +2813,11 @@
       <c r="X41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,59 +2884,62 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E43" s="3">
         <v>40600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>40500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>41200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>46100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>42900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>49900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>46100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>48600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>55500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>30000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>31700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>18100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9100</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2862,8 +2955,11 @@
       <c r="X43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2930,8 +3026,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2998,8 +3097,11 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3066,59 +3168,62 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>907600</v>
+      </c>
+      <c r="E47" s="3">
         <v>1162200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1240600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1046500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>916100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1063100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1094300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>782000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>704600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>673300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>319200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>192500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>110800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>82000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>104400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>151300</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3134,59 +3239,62 @@
       <c r="X47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E48" s="3">
         <v>92500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>97300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>125300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>127400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>130400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>130500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>128500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>126400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>123000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>120400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>88900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>29800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>27400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>28300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>23000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3202,50 +3310,53 @@
       <c r="X48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>77100</v>
+      </c>
+      <c r="E49" s="3">
         <v>77300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>78400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>79500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>80600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>81600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>82700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>83800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>84800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>85900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>87000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>87800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>89000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3261,8 +3372,8 @@
       <c r="U49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,59 +3523,62 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E52" s="3">
         <v>161600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>117400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>119500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>83800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>86900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>126800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>169500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>146400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>283700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>234600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>148200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>126200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>93300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>66500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>60500</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,59 +3665,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1820200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1927700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2017100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2001800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1763700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1821700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1936100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1915300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1917000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1987600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1820500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1606100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>904600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>488600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>477300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>309800</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,59 +3792,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>79400</v>
+      </c>
+      <c r="E57" s="3">
         <v>69100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>66200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>58600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>51000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>47600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>109500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>104800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>127700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>150100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>114200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>93700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>94300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>64600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>59300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>45200</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3730,8 +3861,11 @@
       <c r="X57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3772,16 +3906,16 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>20500</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>16</v>
+      <c r="R58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>16</v>
@@ -3792,65 +3926,68 @@
       <c r="V58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>213700</v>
+      </c>
+      <c r="E59" s="3">
         <v>223900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>262000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>288100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>133600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>131500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>146100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>149200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>154700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>169800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>185900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>128700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>67000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>44700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>44200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>29900</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3866,8 +4003,11 @@
       <c r="X59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3934,59 +4074,62 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>912700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1005300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1040400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1003400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>930700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1000900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>986400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>918900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>856600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>769200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>695400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>649200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>62600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>100600</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4002,8 +4145,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,59 +4429,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1225500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1314900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1381800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1361000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1125600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1194500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1263600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1196700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1159900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1111100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1013400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>887000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>188500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>168000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>177000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>194600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4552,11 +4720,11 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>162500</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,59 +4811,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-401600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-347200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-282600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-240200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-199900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-171700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-42400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>69000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>98900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>66200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-21800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-59100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-69200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-70200</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,59 +5095,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>594700</v>
+      </c>
+      <c r="E76" s="3">
         <v>612800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>635300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>640800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>638100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>627200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>672400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>718600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>757100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>876500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>807100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>719100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>716100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>320600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>300300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-47300</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-54500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-64600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-42400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-40300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-129300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-55300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-56200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>32700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>58900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>29100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>37300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>9700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,56 +5413,57 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E83" s="3">
         <v>5600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>3700</v>
       </c>
       <c r="J83" s="3">
         <v>3700</v>
       </c>
       <c r="K83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L83" s="3">
         <v>3400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>600</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,56 +5837,59 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E89" s="3">
         <v>52600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-143700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-103400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>162400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-75700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-252900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-101400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-53600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-266800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-11100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>43600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>92800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>43100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>68500</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5691,8 +5908,11 @@
       <c r="X89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,56 +5937,57 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1700</v>
+        <v>-2300</v>
       </c>
       <c r="E91" s="3">
         <v>-1700</v>
       </c>
       <c r="F91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G91" s="3">
         <v>-2900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>16</v>
       </c>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,56 +6148,59 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-76100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-37500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-29900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-24200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-38500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-85100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-24200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>5200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-84400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-40600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>8800</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5989,8 +6219,11 @@
       <c r="X94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,56 +6530,59 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>132300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-43700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>26400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>232800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-65900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>21000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>40500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>41100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-34700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>83100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>50400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>595000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>229300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>123400</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6355,8 +6601,11 @@
       <c r="X100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6423,56 +6672,59 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>121500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-28600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-147200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>105100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>58000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-80600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-297500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-84500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-98300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-178500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>554200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>281500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>24700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>200700</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6489,6 +6741,9 @@
         <v>16</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
   <si>
     <t>UPST</t>
   </si>
@@ -656,327 +656,340 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>127600</v>
+        <v>173000</v>
       </c>
       <c r="E8" s="3">
-        <v>127800</v>
+        <v>139100</v>
       </c>
       <c r="F8" s="3">
-        <v>140300</v>
+        <v>138500</v>
       </c>
       <c r="G8" s="3">
-        <v>134600</v>
+        <v>154400</v>
       </c>
       <c r="H8" s="3">
-        <v>135800</v>
+        <v>144000</v>
       </c>
       <c r="I8" s="3">
-        <v>102900</v>
+        <v>140000</v>
       </c>
       <c r="J8" s="3">
+        <v>110100</v>
+      </c>
+      <c r="K8" s="3">
         <v>146900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>157200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>228200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>314000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>287400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>210400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>187300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>116200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>84400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>62900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>68000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>61100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>47900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>28600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E9" s="3">
         <v>38700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>39400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>36100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>36900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>36800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>40600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>43500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>45000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>51100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>48400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>41000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>35000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>24200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>88900</v>
+        <v>133700</v>
       </c>
       <c r="E10" s="3">
-        <v>88400</v>
+        <v>100400</v>
       </c>
       <c r="F10" s="3">
-        <v>104200</v>
+        <v>99100</v>
       </c>
       <c r="G10" s="3">
-        <v>97700</v>
+        <v>118300</v>
       </c>
       <c r="H10" s="3">
-        <v>99000</v>
+        <v>107100</v>
       </c>
       <c r="I10" s="3">
-        <v>62300</v>
+        <v>103300</v>
       </c>
       <c r="J10" s="3">
+        <v>69500</v>
+      </c>
+      <c r="K10" s="3">
         <v>103400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>112200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>177100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>265600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>246400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>175400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>163100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>98800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>71600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>53500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>59200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>52700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>41200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>23200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,79 +1015,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E12" s="3">
         <v>58500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>63100</v>
       </c>
-      <c r="F12" s="3">
-        <v>57200</v>
-      </c>
       <c r="G12" s="3">
+        <v>75300</v>
+      </c>
+      <c r="H12" s="3">
         <v>54900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>58000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>110100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>64000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>66200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>57000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>50000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>46500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>37100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>31400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>14200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1144,31 +1161,34 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+        <v>-33400</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>-18100</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1215,31 +1235,34 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>207300</v>
+      </c>
+      <c r="E17" s="3">
         <v>183100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>195300</v>
       </c>
-      <c r="F17" s="3">
-        <v>187800</v>
-      </c>
       <c r="G17" s="3">
+        <v>205900</v>
+      </c>
+      <c r="H17" s="3">
         <v>178400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>169100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>234800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>205400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>215300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>260300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>279100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>227000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>181800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>151000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>100600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>74000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>53200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>28700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>63400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>59100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>47500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>34100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-55500</v>
+        <v>-34300</v>
       </c>
       <c r="E18" s="3">
-        <v>-67500</v>
+        <v>-44000</v>
       </c>
       <c r="F18" s="3">
-        <v>-47500</v>
+        <v>-56800</v>
       </c>
       <c r="G18" s="3">
-        <v>-43800</v>
+        <v>-51600</v>
       </c>
       <c r="H18" s="3">
-        <v>-33300</v>
+        <v>-34400</v>
       </c>
       <c r="I18" s="3">
-        <v>-131900</v>
+        <v>-29100</v>
       </c>
       <c r="J18" s="3">
+        <v>-124700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-58500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-58100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-32100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>60400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>28600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>36300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>15600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-15400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1479,173 +1512,180 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>1100</v>
+        <v>-5100</v>
       </c>
       <c r="E20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G20" s="3">
+        <v>15200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="K20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="T20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U20" s="3">
+        <v>9300</v>
+      </c>
+      <c r="V20" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="W20" s="3">
         <v>2900</v>
       </c>
-      <c r="F20" s="3">
-        <v>5200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>3500</v>
-      </c>
-      <c r="H20" s="3">
-        <v>5200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K20" s="3">
-        <v>1900</v>
-      </c>
-      <c r="L20" s="3">
-        <v>2200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>9300</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="V20" s="3">
-        <v>2900</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-49600</v>
+        <v>-23900</v>
       </c>
       <c r="E21" s="3">
-        <v>-59000</v>
+        <v>-37400</v>
       </c>
       <c r="F21" s="3">
-        <v>-33200</v>
+        <v>-47400</v>
       </c>
       <c r="G21" s="3">
-        <v>-35400</v>
+        <v>-57700</v>
       </c>
       <c r="H21" s="3">
-        <v>-23700</v>
+        <v>-26000</v>
       </c>
       <c r="I21" s="3">
-        <v>-122800</v>
+        <v>-18600</v>
       </c>
       <c r="J21" s="3">
+        <v>-114900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-52100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-52500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>35500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>61800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>30000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>38300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W21" s="3">
         <v>5700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>100</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>11500</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>14100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>9400</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1692,79 +1732,85 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-54500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-64600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-42300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-40300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-28100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-129200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-55700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-56200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-29800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>32700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>59300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>27800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>36300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>9700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1775,11 +1821,11 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
@@ -1787,11 +1833,11 @@
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-500</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1799,23 +1845,23 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -1823,19 +1869,22 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-54500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-64600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-42400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-40300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-28200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-129300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-55300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-56200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-29900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>32700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>58900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>29100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>37300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-54500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-64600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-42400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-40300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-28200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-129300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-55300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-56200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-29900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>32700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>58900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>29100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>37300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>9700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2398,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1100</v>
+        <v>5100</v>
       </c>
       <c r="E32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="H32" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="N32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P32" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>5300</v>
+      </c>
+      <c r="S32" s="3">
+        <v>9000</v>
+      </c>
+      <c r="T32" s="3">
+        <v>100</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="V32" s="3">
+        <v>3600</v>
+      </c>
+      <c r="W32" s="3">
         <v>-2900</v>
       </c>
-      <c r="F32" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>2100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>700</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>5300</v>
-      </c>
-      <c r="R32" s="3">
-        <v>9000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="U32" s="3">
-        <v>3600</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-54500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-64600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-42400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-40300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-28200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-129300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-55300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-56200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-29900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>32700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>58900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>29100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>37300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>9700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-54500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-64600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-42400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-40300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-28200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-129300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-55300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-56200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-29900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>32700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>58900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>29100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>37300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>9700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,62 +2831,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>445300</v>
+      </c>
+      <c r="E41" s="3">
         <v>374800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>300500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>368400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>516600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>443700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>386900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>422400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>684000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>790400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>757800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>986600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1041500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>506300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>257000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>250800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>53200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2816,8 +2903,11 @@
       <c r="Y41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,62 +2977,65 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>40000</v>
+        <v>666400</v>
       </c>
       <c r="E43" s="3">
-        <v>40600</v>
+        <v>832300</v>
       </c>
       <c r="F43" s="3">
-        <v>40500</v>
+        <v>1094200</v>
       </c>
       <c r="G43" s="3">
-        <v>41200</v>
+        <v>1171300</v>
       </c>
       <c r="H43" s="3">
+        <v>975100</v>
+      </c>
+      <c r="I43" s="3">
+        <v>841500</v>
+      </c>
+      <c r="J43" s="3">
+        <v>987200</v>
+      </c>
+      <c r="K43" s="3">
+        <v>46700</v>
+      </c>
+      <c r="L43" s="3">
+        <v>49900</v>
+      </c>
+      <c r="M43" s="3">
         <v>46100</v>
       </c>
-      <c r="I43" s="3">
-        <v>42900</v>
-      </c>
-      <c r="J43" s="3">
-        <v>46700</v>
-      </c>
-      <c r="K43" s="3">
-        <v>49900</v>
-      </c>
-      <c r="L43" s="3">
-        <v>46100</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>48600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>55500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>30000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>31700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>18100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9100</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2958,31 +3051,34 @@
       <c r="Y43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3029,31 +3125,34 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -3100,31 +3199,34 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>1322200</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>1392900</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>1533400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>1639000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>1590200</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>1351400</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>1439100</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -3171,62 +3273,65 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>907600</v>
+        <v>43400</v>
       </c>
       <c r="E47" s="3">
-        <v>1162200</v>
+        <v>46400</v>
       </c>
       <c r="F47" s="3">
-        <v>1240600</v>
+        <v>47200</v>
       </c>
       <c r="G47" s="3">
-        <v>1046500</v>
+        <v>47200</v>
       </c>
       <c r="H47" s="3">
-        <v>916100</v>
+        <v>51000</v>
       </c>
       <c r="I47" s="3">
-        <v>1063100</v>
+        <v>41300</v>
       </c>
       <c r="J47" s="3">
+        <v>41300</v>
+      </c>
+      <c r="K47" s="3">
         <v>1094300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>782000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>704600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>673300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>319200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>192500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>110800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>82000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>104400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>151300</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3242,62 +3347,65 @@
       <c r="Y47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>55200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>59100</v>
+      </c>
+      <c r="F48" s="3">
+        <v>62800</v>
+      </c>
+      <c r="G48" s="3">
+        <v>66000</v>
+      </c>
+      <c r="H48" s="3">
+        <v>92900</v>
+      </c>
+      <c r="I48" s="3">
+        <v>96700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>100500</v>
+      </c>
+      <c r="K48" s="3">
+        <v>130500</v>
+      </c>
+      <c r="L48" s="3">
+        <v>128500</v>
+      </c>
+      <c r="M48" s="3">
+        <v>126400</v>
+      </c>
+      <c r="N48" s="3">
+        <v>123000</v>
+      </c>
+      <c r="O48" s="3">
+        <v>120400</v>
+      </c>
+      <c r="P48" s="3">
         <v>88900</v>
       </c>
-      <c r="E48" s="3">
-        <v>92500</v>
-      </c>
-      <c r="F48" s="3">
-        <v>97300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>125300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>127400</v>
-      </c>
-      <c r="I48" s="3">
-        <v>130400</v>
-      </c>
-      <c r="J48" s="3">
-        <v>130500</v>
-      </c>
-      <c r="K48" s="3">
-        <v>128500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>126400</v>
-      </c>
-      <c r="M48" s="3">
-        <v>123000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>120400</v>
-      </c>
-      <c r="O48" s="3">
-        <v>88900</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>29800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>27400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>28300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>23000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3313,53 +3421,56 @@
       <c r="Y48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>77100</v>
+        <v>106200</v>
       </c>
       <c r="E49" s="3">
-        <v>77300</v>
+        <v>106900</v>
       </c>
       <c r="F49" s="3">
-        <v>78400</v>
+        <v>107000</v>
       </c>
       <c r="G49" s="3">
-        <v>79500</v>
+        <v>109700</v>
       </c>
       <c r="H49" s="3">
-        <v>80600</v>
+        <v>111900</v>
       </c>
       <c r="I49" s="3">
-        <v>81600</v>
+        <v>97800</v>
       </c>
       <c r="J49" s="3">
+        <v>111500</v>
+      </c>
+      <c r="K49" s="3">
         <v>82700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>83800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>84800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>85900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>87000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>87800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>89000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3375,8 +3486,8 @@
       <c r="V49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,62 +3643,65 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>204000</v>
+        <v>204400</v>
       </c>
       <c r="E52" s="3">
-        <v>161600</v>
+        <v>166700</v>
       </c>
       <c r="F52" s="3">
-        <v>117400</v>
+        <v>136600</v>
       </c>
       <c r="G52" s="3">
-        <v>119500</v>
+        <v>114600</v>
       </c>
       <c r="H52" s="3">
-        <v>83800</v>
+        <v>114600</v>
       </c>
       <c r="I52" s="3">
-        <v>86900</v>
+        <v>130600</v>
       </c>
       <c r="J52" s="3">
+        <v>86400</v>
+      </c>
+      <c r="K52" s="3">
         <v>126800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>169500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>146400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>283700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>234600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>148200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>126200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>93300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>66500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>60500</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,62 +3791,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1809000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1820200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1927700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2017100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2001800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1763700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1821700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1936100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1915300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1917000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1987600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1820500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1606100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>904600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>488600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>477300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>309800</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3739,8 +3865,11 @@
       <c r="Y54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,62 +3923,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>79400</v>
+        <v>22600</v>
       </c>
       <c r="E57" s="3">
-        <v>69100</v>
+        <v>13900</v>
       </c>
       <c r="F57" s="3">
-        <v>66200</v>
+        <v>10000</v>
       </c>
       <c r="G57" s="3">
-        <v>58600</v>
+        <v>12600</v>
       </c>
       <c r="H57" s="3">
-        <v>51000</v>
+        <v>7000</v>
       </c>
       <c r="I57" s="3">
-        <v>47600</v>
+        <v>6900</v>
       </c>
       <c r="J57" s="3">
+        <v>6600</v>
+      </c>
+      <c r="K57" s="3">
         <v>109500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>104800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>127700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>150100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>114200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>93700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>94300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>64600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>59300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>45200</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3864,31 +3995,34 @@
       <c r="Y57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>17100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3909,16 +4043,16 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>20500</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>16</v>
+      <c r="S58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>16</v>
@@ -3929,68 +4063,71 @@
       <c r="W58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>213700</v>
-      </c>
-      <c r="E59" s="3">
-        <v>223900</v>
-      </c>
-      <c r="F59" s="3">
-        <v>262000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>288100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>133600</v>
-      </c>
-      <c r="I59" s="3">
-        <v>131500</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K59" s="3">
         <v>146100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>149200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>154700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>169800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>185900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>128700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>67000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>44700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>44200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>29900</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4006,31 +4143,34 @@
       <c r="Y59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>98600</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>70500</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>62500</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>92100</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>58400</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>68200</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -4077,62 +4217,65 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>912700</v>
+        <v>1037300</v>
       </c>
       <c r="E61" s="3">
-        <v>1005300</v>
+        <v>1075300</v>
       </c>
       <c r="F61" s="3">
-        <v>1040400</v>
+        <v>1182500</v>
       </c>
       <c r="G61" s="3">
-        <v>1003400</v>
+        <v>1229200</v>
       </c>
       <c r="H61" s="3">
-        <v>930700</v>
+        <v>1246700</v>
       </c>
       <c r="I61" s="3">
-        <v>1000900</v>
+        <v>1009800</v>
       </c>
       <c r="J61" s="3">
+        <v>1088500</v>
+      </c>
+      <c r="K61" s="3">
         <v>986400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>918900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>856600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>769200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>695400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>649200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>62600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>100600</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4148,31 +4291,34 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>77600</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>79800</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>69900</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>60500</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>55900</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>47600</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,62 +4587,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1213400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1225500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1314900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1381800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1361000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1125600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1194500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1263600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1196700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1159900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1111100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1013400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>887000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>188500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>168000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>177000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>194600</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4503,8 +4661,11 @@
       <c r="Y66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4723,11 +4891,11 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>162500</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,62 +4985,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-408400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-401600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-347200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-282600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-240200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-199900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-171700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-42400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>69000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>98900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>66200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-59100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-69200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-70200</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4885,8 +5059,11 @@
       <c r="Y72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,62 +5281,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>595500</v>
+      </c>
+      <c r="E76" s="3">
         <v>594700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>612800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>635300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>640800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>638100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>627200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>672400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>718600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>757100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>876500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>807100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>719100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>716100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>320600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>300300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-47300</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5169,8 +5355,11 @@
       <c r="Y76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-54500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-64600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-42400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-40300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-28200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-129300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-55300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-56200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-29900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>32700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>58900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>29100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>37300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>9700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,59 +5612,60 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4800</v>
+        <v>3800</v>
       </c>
       <c r="E83" s="3">
-        <v>5600</v>
+        <v>3400</v>
       </c>
       <c r="F83" s="3">
-        <v>9100</v>
+        <v>5300</v>
       </c>
       <c r="G83" s="3">
-        <v>4900</v>
+        <v>2600</v>
       </c>
       <c r="H83" s="3">
-        <v>4400</v>
+        <v>1600</v>
       </c>
       <c r="I83" s="3">
-        <v>6400</v>
+        <v>3400</v>
       </c>
       <c r="J83" s="3">
-        <v>3700</v>
+        <v>1700</v>
       </c>
       <c r="K83" s="3">
         <v>3700</v>
       </c>
       <c r="L83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M83" s="3">
         <v>3400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>600</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5485,8 +5684,11 @@
       <c r="Y83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,59 +6054,62 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>179300</v>
+      </c>
+      <c r="E89" s="3">
         <v>65300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>52600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-143700</v>
       </c>
-      <c r="G89" s="3">
-        <v>-103400</v>
-      </c>
       <c r="H89" s="3">
-        <v>162400</v>
+        <v>-107700</v>
       </c>
       <c r="I89" s="3">
+        <v>217300</v>
+      </c>
+      <c r="J89" s="3">
         <v>-75700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-252900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-101400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-53600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-266800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-11100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>43600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>92800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>43100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>68500</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5911,8 +6128,11 @@
       <c r="Y89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,59 +6158,60 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2300</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1700</v>
       </c>
-      <c r="F91" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>16</v>
       </c>
@@ -6009,8 +6230,11 @@
       <c r="Y91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,59 +6378,62 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-46200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-76100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-37500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-29900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-24200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-38500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-25900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-85100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-24200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>5200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-84400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-40600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>8800</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6222,8 +6452,11 @@
       <c r="Y94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,31 +6482,32 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,59 +6776,62 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E100" s="3">
         <v>132300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-43700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>26400</v>
       </c>
-      <c r="G100" s="3">
-        <v>232800</v>
-      </c>
       <c r="H100" s="3">
-        <v>-65900</v>
+        <v>237100</v>
       </c>
       <c r="I100" s="3">
+        <v>-120800</v>
+      </c>
+      <c r="J100" s="3">
         <v>21000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>40500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>41100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-34700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>83100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>50400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>595000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>229300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-19300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>123400</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6604,31 +6850,34 @@
       <c r="Y100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6675,59 +6924,62 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E102" s="3">
         <v>121500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-28600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-147200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>105100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>58000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-80600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-297500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-84500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-98300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-178500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>554200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>281500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>24700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>200700</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6744,6 +6996,9 @@
         <v>16</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
   <si>
     <t>UPST</t>
   </si>
@@ -656,340 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>226400</v>
+      </c>
+      <c r="E8" s="3">
         <v>173000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>139100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>138500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>154400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>144000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>140000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>110100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>146900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>157200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>228200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>314000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>287400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>210400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>187300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>116200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>84400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>62900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>68000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>61100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>47900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>28600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E9" s="3">
         <v>39300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>38700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>39400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>36100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>36900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>36800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>40600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>43500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>45000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>51100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>48400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>41000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>35000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>24200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>17400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>185800</v>
+      </c>
+      <c r="E10" s="3">
         <v>133700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>99100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>118300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>107100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>103300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>69500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>103400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>112200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>177100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>265600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>246400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>175400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>163100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>98800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>71600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>53500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>59200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>52700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>41200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>23200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,82 +1028,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>67200</v>
+      </c>
+      <c r="E12" s="3">
         <v>64900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>58500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>63100</v>
       </c>
-      <c r="G12" s="3">
-        <v>75300</v>
-      </c>
       <c r="H12" s="3">
+        <v>57200</v>
+      </c>
+      <c r="I12" s="3">
         <v>54900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>58000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>110100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>64000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>66200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>57000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>50000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>46500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>37100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>31400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>19000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1164,22 +1180,25 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>-33400</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="3">
-        <v>-18100</v>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>16</v>
@@ -1190,8 +1209,8 @@
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1238,35 +1257,38 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E15" s="3">
         <v>5400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1312,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>223700</v>
+      </c>
+      <c r="E17" s="3">
         <v>207300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>183100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>195300</v>
       </c>
-      <c r="G17" s="3">
-        <v>205900</v>
-      </c>
       <c r="H17" s="3">
+        <v>187800</v>
+      </c>
+      <c r="I17" s="3">
         <v>178400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>169100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>234800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>205400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>215300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>260300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>279100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>227000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>181800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>151000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>100600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>74000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>53200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>28700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>63400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>59100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>47500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>34100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-34300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-44000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-56800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-51600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-34400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-29100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-124700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-58500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-58100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-32100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>34900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>60400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>28600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>36300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-15400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1513,183 +1545,190 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3700</v>
       </c>
-      <c r="G20" s="3">
-        <v>15200</v>
-      </c>
       <c r="H20" s="3">
+        <v>12900</v>
+      </c>
+      <c r="I20" s="3">
         <v>-3500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-5300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>9300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-23900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-37400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-47400</v>
       </c>
-      <c r="G21" s="3">
-        <v>-57700</v>
-      </c>
       <c r="H21" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-26000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-18600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-114900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-52100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-52500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-26500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>35500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>61800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>30000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>38300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X21" s="3">
         <v>5700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E22" s="3">
         <v>10800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1735,87 +1774,93 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-54500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-64600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-42300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-40300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-28100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-129200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-55700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-56200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-29800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>32700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>59300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>27800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>36300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>10300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>9700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1824,11 +1869,11 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -1836,11 +1881,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-500</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1848,23 +1893,23 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -1872,19 +1917,22 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-54500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-64600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-42400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-40300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-28200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-129300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-55300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-56200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-29900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>32700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>58900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>29100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>37300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-54500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-64600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-42400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-40300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-28200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-129300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-55300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-56200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-29900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>32700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>58900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>29100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>37300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>9700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E32" s="3">
         <v>5100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3700</v>
       </c>
-      <c r="G32" s="3">
-        <v>-15200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="I32" s="3">
         <v>3500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>5300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-9300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-54500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-64600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-42400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-40300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-28200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-129300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-55300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-56200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-29900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>32700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>58900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>29100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>37300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>9700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-54500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-64600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-42400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-40300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-28200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-129300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-55300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-56200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-29900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>32700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>58900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>29100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>37300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>9700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,65 +2917,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>788400</v>
+      </c>
+      <c r="E41" s="3">
         <v>445300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>374800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>300500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>368400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>516600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>443700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>386900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>422400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>684000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>790400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>757800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>986600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1041500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>506300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>257000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>250800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>53200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2906,16 +2992,19 @@
       <c r="Z41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2924,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -2980,65 +3069,68 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>666400</v>
+        <v>932900</v>
       </c>
       <c r="E43" s="3">
+        <v>744000</v>
+      </c>
+      <c r="F43" s="3">
         <v>832300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1094200</v>
       </c>
-      <c r="G43" s="3">
-        <v>1171300</v>
-      </c>
       <c r="H43" s="3">
+        <v>1211800</v>
+      </c>
+      <c r="I43" s="3">
         <v>975100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>841500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>987200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>46700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>49900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>46100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>48600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>55500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>30000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>31700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>18100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9100</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3054,8 +3146,11 @@
       <c r="Z43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3080,8 +3175,8 @@
       <c r="J44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3128,8 +3223,11 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3154,8 +3252,8 @@
       <c r="J45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -3202,35 +3300,38 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1322200</v>
+        <v>1945000</v>
       </c>
       <c r="E46" s="3">
+        <v>1426400</v>
+      </c>
+      <c r="F46" s="3">
         <v>1392900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1533400</v>
       </c>
-      <c r="G46" s="3">
-        <v>1639000</v>
-      </c>
       <c r="H46" s="3">
+        <v>1712400</v>
+      </c>
+      <c r="I46" s="3">
         <v>1590200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1351400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1439100</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -3276,65 +3377,68 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>43400</v>
+        <v>41300</v>
       </c>
       <c r="E47" s="3">
+        <v>41300</v>
+      </c>
+      <c r="F47" s="3">
         <v>46400</v>
-      </c>
-      <c r="F47" s="3">
-        <v>47200</v>
       </c>
       <c r="G47" s="3">
         <v>47200</v>
       </c>
       <c r="H47" s="3">
+        <v>41300</v>
+      </c>
+      <c r="I47" s="3">
         <v>51000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>41300</v>
       </c>
       <c r="J47" s="3">
         <v>41300</v>
       </c>
       <c r="K47" s="3">
+        <v>41300</v>
+      </c>
+      <c r="L47" s="3">
         <v>1094300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>782000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>704600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>673300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>319200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>192500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>110800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>82000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>104400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>151300</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3350,65 +3454,68 @@
       <c r="Z47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E48" s="3">
         <v>55200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>59100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>62800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>66000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>92900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>96700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>100500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>130500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>128500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>126400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>123000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>120400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>88900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>29800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>27400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>28300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>23000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3424,56 +3531,59 @@
       <c r="Z48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>107500</v>
+      </c>
+      <c r="E49" s="3">
         <v>106200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>106900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>107000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>109700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>111900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>97800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>111500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>82700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>83800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>84800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>85900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>87000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>87800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>89000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3489,8 +3599,8 @@
       <c r="W49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -3498,8 +3608,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,65 +3762,68 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>204400</v>
+        <v>221700</v>
       </c>
       <c r="E52" s="3">
+        <v>179900</v>
+      </c>
+      <c r="F52" s="3">
         <v>166700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>136600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>87700</v>
+      </c>
+      <c r="I52" s="3">
         <v>114600</v>
       </c>
-      <c r="H52" s="3">
-        <v>114600</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>130600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>86400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>126800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>169500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>146400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>283700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>234600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>148200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>126200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>93300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>66500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>60500</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3720,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,65 +3916,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2367000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1809000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1820200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1927700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2017100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2001800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1763700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1821700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1936100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1915300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1917000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1987600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1820500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1606100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>904600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>488600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>477300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>309800</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3868,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,65 +4053,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E57" s="3">
         <v>22600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>109500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>104800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>127700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>150100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>114200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>93700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>94300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>64600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>59300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>45200</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3998,35 +4128,38 @@
       <c r="Z57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E58" s="3">
         <v>3800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11200</v>
       </c>
-      <c r="G58" s="3">
-        <v>15000</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>3800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4046,16 +4179,16 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>20500</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>16</v>
+      <c r="T58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>16</v>
@@ -4066,14 +4199,17 @@
       <c r="X58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4098,39 +4234,39 @@
       <c r="J59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L59" s="3">
         <v>146100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>149200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>154700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>169800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>185900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>128700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>67000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>44700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>44200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>29900</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4146,35 +4282,38 @@
       <c r="Z59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>135900</v>
+      </c>
+      <c r="E60" s="3">
         <v>98600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>70500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>62500</v>
       </c>
-      <c r="G60" s="3">
-        <v>92100</v>
-      </c>
       <c r="H60" s="3">
+        <v>77200</v>
+      </c>
+      <c r="I60" s="3">
         <v>58400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>68200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>58000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -4220,65 +4359,68 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1524400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1037300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1075300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1182500</v>
       </c>
-      <c r="G61" s="3">
-        <v>1229200</v>
-      </c>
       <c r="H61" s="3">
+        <v>1244200</v>
+      </c>
+      <c r="I61" s="3">
         <v>1246700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1009800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1088500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>986400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>918900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>856600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>769200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>695400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>649200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>62600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>100600</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4294,35 +4436,38 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>73500</v>
+      </c>
+      <c r="E62" s="3">
         <v>77600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>79800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>69900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>60500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>55900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>47600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>48000</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -4368,8 +4513,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,65 +4744,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1733700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1213400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1225500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1314900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1381800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1361000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1125600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1194500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1263600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1196700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1159900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1111100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1013400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>887000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>188500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>168000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>177000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>194600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4664,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4894,11 +5061,11 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>162500</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4914,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,65 +5158,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-411200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-408400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-401600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-347200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-282600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-240200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-199900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-171700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-42400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>69000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>98900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>66200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-21800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-59100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-69200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-70200</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5062,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,65 +5466,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>633200</v>
+      </c>
+      <c r="E76" s="3">
         <v>595500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>594700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>612800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>635300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>640800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>638100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>627200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>672400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>718600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>757100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>876500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>807100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>719100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>716100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>320600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>300300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-47300</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5358,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-54500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-64600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-42400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-40300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-28200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-129300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-55300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-56200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-29900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>32700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>58900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>29100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>37300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>9700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,62 +5810,63 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>3700</v>
       </c>
       <c r="L83" s="3">
         <v>3700</v>
       </c>
       <c r="M83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N83" s="3">
         <v>3400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>600</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5687,8 +5885,11 @@
       <c r="Z83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,62 +6270,65 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-110900</v>
+      </c>
+      <c r="E89" s="3">
         <v>179300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>65300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>52600</v>
       </c>
-      <c r="G89" s="3">
-        <v>-143700</v>
-      </c>
       <c r="H89" s="3">
+        <v>-145600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-107700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>217300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-75700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-252900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-101400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-53600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-266800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-11100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>43600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>92800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>43100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>68500</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6131,8 +6347,11 @@
       <c r="Z89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,62 +6378,63 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>16</v>
       </c>
@@ -6233,8 +6453,11 @@
       <c r="Z91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,62 +6607,65 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-77900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-46200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-76100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-37500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-29900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-24200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-38500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-85100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-24200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>5200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-84400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-40600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>8800</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6455,8 +6684,11 @@
       <c r="Z94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6509,8 +6742,8 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6557,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,62 +7021,65 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>509300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-38000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>132300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-43700</v>
       </c>
-      <c r="G100" s="3">
-        <v>26400</v>
-      </c>
       <c r="H100" s="3">
+        <v>28300</v>
+      </c>
+      <c r="I100" s="3">
         <v>237100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-120800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>21000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>40500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>41100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-34700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>83100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>50400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>595000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>229300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-19300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>123400</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6853,8 +7098,11 @@
       <c r="Z100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6879,8 +7127,8 @@
       <c r="J101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6927,62 +7175,65 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>320500</v>
+      </c>
+      <c r="E102" s="3">
         <v>95100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>121500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-28600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-147200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>105100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>58000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-80600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-297500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-84500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-98300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-178500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>554200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>281500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>24700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>200700</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6999,6 +7250,9 @@
         <v>16</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
   <si>
     <t>UPST</t>
   </si>
@@ -656,352 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>220400</v>
+      </c>
+      <c r="E8" s="3">
         <v>226400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>173000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>139100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>138500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>154400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>144000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>140000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>110100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>146900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>157200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>228200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>314000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>287400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>210400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>187300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>116200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>84400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>62900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>68000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>61100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>47900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>28600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E9" s="3">
         <v>40600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>39300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>38700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>39400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>36100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>36900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>36800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>40600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>43500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>45000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>51100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>48400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>41000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>35000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>24200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>17400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>179900</v>
+      </c>
+      <c r="E10" s="3">
         <v>185800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>133700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>100400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>99100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>118300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>107100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>103300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>69500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>103400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>112200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>177100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>265600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>246400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>175400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>163100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>98800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>71600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>53500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>59200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>52700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>41200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>23200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E12" s="3">
         <v>67200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>64900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>58500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>63100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>57200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>54900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>58000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>110100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>64000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>66200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>57000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>50000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>46500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>37100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>31400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>19000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>14200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>5100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1183,20 +1200,23 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-33400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1212,8 +1232,8 @@
       <c r="K14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1260,38 +1280,41 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E15" s="3">
         <v>4700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6400</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>217900</v>
+      </c>
+      <c r="E17" s="3">
         <v>223700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>207300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>183100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>195300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>187800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>178400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>169100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>234800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>205400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>215300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>260300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>279100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>227000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>181800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>151000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>100600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>74000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>53200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>28700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>63400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>59100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>47500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>34100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E18" s="3">
         <v>2700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-34300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-44000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-56800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-33400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-34400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-29100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-124700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-58500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-58100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-32100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>34900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>60400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>28600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>36300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>15600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-15400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1546,192 +1579,199 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E20" s="3">
         <v>13500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3700</v>
-      </c>
       <c r="H20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I20" s="3">
         <v>12900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-700</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-5300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-9000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>4000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-23900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-37400</v>
       </c>
-      <c r="G21" s="3">
-        <v>-47400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-48200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-37300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-18600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-114900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-52100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-52500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-26500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>35500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>61800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>30000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>38300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y21" s="3">
         <v>5700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>100</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E22" s="3">
         <v>7400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1777,94 +1817,100 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-54500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-64600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-42300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-40300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-28100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-129200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-55700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-56200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-29800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>32700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>59300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>27800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>36300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>9700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -1872,11 +1918,11 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1884,11 +1930,11 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-500</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1896,23 +1942,23 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -1920,19 +1966,22 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-54500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-64600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-42400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-40300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-28200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-129300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-55300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-56200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-29900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>32700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>58900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>29100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>37300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-54500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-64600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-42400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-40300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-28200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-129300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-55300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-56200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-29900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>32700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>58900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>29100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>37300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>9700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,162 +2537,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-13500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3">
-        <v>3700</v>
-      </c>
       <c r="H32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I32" s="3">
         <v>-12900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>700</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>5300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>9000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-54500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-64600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-42400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-40300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-28200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-129300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-55300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-56200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-29900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>32700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>58900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>29100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>37300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>9700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-54500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-64600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-42400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-40300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-28200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-129300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-55300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-56200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-29900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>32700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>58900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>29100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>37300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>9700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,68 +3004,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>599800</v>
+      </c>
+      <c r="E41" s="3">
         <v>788400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>445300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>374800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>300500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>368400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>516600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>443700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>386900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>422400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>684000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>790400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>757800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>986600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1041500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>506300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>257000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>250800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>53200</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2995,29 +3082,32 @@
       <c r="AA41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E42" s="3">
         <v>7000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7100</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>14900</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -3072,68 +3162,71 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>958900</v>
+      </c>
+      <c r="E43" s="3">
         <v>932900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>744000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>832300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1094200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1211800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>975100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>841500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>987200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>46700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>49900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>46100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>48600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>55500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>30000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>31700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>18100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9100</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3149,8 +3242,11 @@
       <c r="AA43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3178,8 +3274,8 @@
       <c r="K44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3226,8 +3322,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3255,8 +3354,8 @@
       <c r="K45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -3303,38 +3402,41 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1833300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1945000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1426400</v>
       </c>
-      <c r="F46" s="3">
-        <v>1392900</v>
-      </c>
       <c r="G46" s="3">
+        <v>1415900</v>
+      </c>
+      <c r="H46" s="3">
         <v>1533400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1712400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1590200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1351400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1439100</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -3380,8 +3482,11 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3392,56 +3497,56 @@
         <v>41300</v>
       </c>
       <c r="F47" s="3">
+        <v>41300</v>
+      </c>
+      <c r="G47" s="3">
         <v>46400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>47200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>41300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>51000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>41300</v>
       </c>
       <c r="K47" s="3">
         <v>41300</v>
       </c>
       <c r="L47" s="3">
+        <v>41300</v>
+      </c>
+      <c r="M47" s="3">
         <v>1094300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>782000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>704600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>673300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>319200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>192500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>110800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>82000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>104400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>151300</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3457,68 +3562,71 @@
       <c r="AA47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E48" s="3">
         <v>51500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>55200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>59100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>62800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>66000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>92900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>96700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>100500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>130500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>128500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>126400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>123000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>120400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>88900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>29800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>27400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>28300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>23000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3534,59 +3642,62 @@
       <c r="AA48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>111400</v>
+      </c>
+      <c r="E49" s="3">
         <v>107500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>106200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>106900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>107000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>109700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>111900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>97800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>111500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>82700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>83800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>84800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>85900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>87000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>87800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>89000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3602,8 +3713,8 @@
       <c r="X49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,68 +3882,71 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>262500</v>
+      </c>
+      <c r="E52" s="3">
         <v>221700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>179900</v>
       </c>
-      <c r="F52" s="3">
-        <v>166700</v>
-      </c>
       <c r="G52" s="3">
+        <v>143700</v>
+      </c>
+      <c r="H52" s="3">
         <v>136600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>87700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>114600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>130600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>86400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>126800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>169500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>146400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>283700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>234600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>148200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>126200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>93300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>66500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>60500</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,68 +4042,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2296300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2367000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1809000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1820200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1927700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2017100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2001800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1763700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1821700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1936100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1915300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1917000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1987600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1820500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1606100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>904600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>488600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>477300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>309800</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,68 +4184,69 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E57" s="3">
         <v>12400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>22600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>109500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>104800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>127700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>150100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>114200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>93700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>94300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>64600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>59300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>45200</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4131,38 +4262,41 @@
       <c r="AA57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E58" s="3">
         <v>15400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11200</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>3800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4182,16 +4316,16 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>20500</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>16</v>
+      <c r="U58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>16</v>
@@ -4202,14 +4336,17 @@
       <c r="Y58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4237,39 +4374,39 @@
       <c r="K59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M59" s="3">
         <v>146100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>149200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>154700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>169800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>185900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>128700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>67000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>44700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>44200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>29900</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4285,38 +4422,41 @@
       <c r="AA59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>82100</v>
+      </c>
+      <c r="E60" s="3">
         <v>135900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>98600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>70500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>62500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>77200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>58400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>68200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>58000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -4362,68 +4502,71 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1446300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1524400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1037300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1075300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1182500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1244200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1246700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1009800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1088500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>986400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>918900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>856600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>769200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>695400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>649200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>21400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>62600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>100600</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4439,38 +4582,41 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>91200</v>
+      </c>
+      <c r="E62" s="3">
         <v>73500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>77600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>79800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>69900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>60500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>55900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>47600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>48000</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,68 +4902,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1619600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1733700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1213400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1225500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1314900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1381800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1361000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1125600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1194500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1263600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1196700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1159900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1111100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1013400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>887000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>188500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>168000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>177000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>194600</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4824,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5064,11 +5232,11 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>162500</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,68 +5332,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-413600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-411200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-408400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-401600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-347200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-282600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-240200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-199900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-171700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-42400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>69000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>98900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>66200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-21800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-59100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-69200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-70200</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,68 +5652,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>676600</v>
+      </c>
+      <c r="E76" s="3">
         <v>633200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>595500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>594700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>612800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>635300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>640800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>638100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>627200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>672400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>718600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>757100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>876500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>807100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>719100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>716100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>320600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>300300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-47300</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5546,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-54500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-64600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-42400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-40300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-28200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-129300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-55300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-56200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-29900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>32700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>58900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>29100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>37300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>9700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,65 +6009,66 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E83" s="3">
         <v>8000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1700</v>
-      </c>
-      <c r="L83" s="3">
-        <v>3700</v>
       </c>
       <c r="M83" s="3">
         <v>3700</v>
       </c>
       <c r="N83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O83" s="3">
         <v>3400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>600</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,65 +6487,68 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-110900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>179300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>65300</v>
       </c>
-      <c r="G89" s="3">
-        <v>52600</v>
-      </c>
       <c r="H89" s="3">
+        <v>44300</v>
+      </c>
+      <c r="I89" s="3">
         <v>-145600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-107700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>217300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-75700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-252900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-101400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-53600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-266800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>43600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>92800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>43100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>68500</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6350,8 +6567,11 @@
       <c r="AA89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,65 +6599,66 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>16</v>
       </c>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,65 +6837,68 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-78600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-77900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-46200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-76100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-37500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-29900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-24200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-38500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-85100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-24200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>5200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-84400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-40600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>8800</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6687,8 +6917,11 @@
       <c r="AA94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6745,8 +6979,8 @@
       <c r="K96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,65 +7267,68 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-44700</v>
+      </c>
+      <c r="E100" s="3">
         <v>509300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-38000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>132300</v>
       </c>
-      <c r="G100" s="3">
-        <v>-43700</v>
-      </c>
       <c r="H100" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="I100" s="3">
         <v>28300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>237100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-120800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>21000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>40500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>41100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-34700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>83100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>50400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>595000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>229300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-19300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>123400</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7101,8 +7347,11 @@
       <c r="AA100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7130,8 +7379,8 @@
       <c r="K101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7178,65 +7427,68 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-136700</v>
+      </c>
+      <c r="E102" s="3">
         <v>320500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>95100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>121500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-28600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-147200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>105100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>58000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-80600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-297500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-84500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-98300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-178500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>19500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>554200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>281500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>24700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>200700</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7253,6 +7505,9 @@
         <v>16</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>UPST</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>265100</v>
+      </c>
+      <c r="E8" s="3">
         <v>220400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>226400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>173000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>139100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>138500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>154400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>144000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>140000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>110100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>146900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>157200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>228200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>314000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>287400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>210400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>187300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>116200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>84400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>62900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>68000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>61100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>47900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>28600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E9" s="3">
         <v>40500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>40600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>39300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>38700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>39400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>36100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>36900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>36800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>40600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>43500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>45000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>51100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>48400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>41000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>35000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>24200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>17400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>218800</v>
+      </c>
+      <c r="E10" s="3">
         <v>179900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>185800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>133700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>100400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>99100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>118300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>107100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>103300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>69500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>103400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>112200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>177100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>265600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>246400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>175400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>163100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>98800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>71600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>53500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>59200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>52700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>41200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>23200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,88 +1056,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>68800</v>
+      </c>
+      <c r="E12" s="3">
         <v>57800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>67200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>64900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>58500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>63100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>57200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>54900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>58000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>110100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>64000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>66200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>57000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>50000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>46500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>37100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>31400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>19000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>14200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>5100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1203,23 +1220,26 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-33400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1235,8 +1255,8 @@
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1283,41 +1303,44 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E15" s="3">
         <v>6400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6400</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>252700</v>
+      </c>
+      <c r="E17" s="3">
         <v>217900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>223700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>207300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>183100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>195300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>187800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>178400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>169100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>234800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>205400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>215300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>260300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>279100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>227000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>181800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>151000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>100600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>74000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>53200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>28700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>63400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>59100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>47500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>34100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E18" s="3">
         <v>2500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-34300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-44000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-56800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-33400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-34400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-29100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-124700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-58500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-58100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-32100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>34900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>60400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>28600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>36300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>15600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-15400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1580,201 +1613,208 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>13500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1800</v>
-      </c>
       <c r="H20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-2900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-700</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-5300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-9000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>9300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E21" s="3">
         <v>11000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-23900</v>
       </c>
-      <c r="G21" s="3">
-        <v>-37400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-48200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-37300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-26000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-18600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-114900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-52100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-52500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-26500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>35500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>61800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>30000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>38300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z21" s="3">
         <v>5700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>100</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E22" s="3">
         <v>7000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1820,88 +1860,94 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-54500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-64600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-42300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-40300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-28100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-129200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-55700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-56200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-29800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>32700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>59300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>27800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>36300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>9700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1909,11 +1955,11 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -1921,11 +1967,11 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1933,11 +1979,11 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-500</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1945,23 +1991,23 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
@@ -1969,19 +2015,22 @@
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-54500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-64600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-42400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-40300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-129300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-55300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-56200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-29900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>32700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>58900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>29100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>37300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-54500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-64600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-42400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-40300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-129300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-55300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-56200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-29900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>32700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>58900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>29100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>37300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>9700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2607,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>2100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-13500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5100</v>
       </c>
-      <c r="G32" s="3">
-        <v>1800</v>
-      </c>
       <c r="H32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I32" s="3">
         <v>2900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>700</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>5300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>9000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-9300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-54500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-64600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-42400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-40300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-129300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-55300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-56200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-29900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>32700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>58900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>29100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>37300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>9700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-54500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-64600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-42400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-40300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-129300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-55300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-56200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-29900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>32700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>58900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>29100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>37300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>9700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,71 +3091,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>395900</v>
+      </c>
+      <c r="E41" s="3">
         <v>599800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>788400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>445300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>374800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>368400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>516600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>443700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>386900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>422400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>684000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>790400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>757800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>986600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1041500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>506300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>257000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>250800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>53200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3085,32 +3172,35 @@
       <c r="AB41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E42" s="3">
         <v>6700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7100</v>
       </c>
-      <c r="G42" s="3">
-        <v>4900</v>
-      </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>14900</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -3165,71 +3255,74 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>958900</v>
+        <v>1118900</v>
       </c>
       <c r="E43" s="3">
-        <v>932900</v>
+        <v>877200</v>
       </c>
       <c r="F43" s="3">
-        <v>744000</v>
+        <v>876600</v>
       </c>
       <c r="G43" s="3">
-        <v>832300</v>
+        <v>712500</v>
       </c>
       <c r="H43" s="3">
+        <v>872300</v>
+      </c>
+      <c r="I43" s="3">
         <v>1094200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1211800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>975100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>841500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>987200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>46700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>49900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>46100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>48600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>55500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>30000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>31700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>18100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9100</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3245,8 +3338,11 @@
       <c r="AB43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3277,8 +3373,8 @@
       <c r="L44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3325,8 +3421,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3357,8 +3456,8 @@
       <c r="L45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -3405,41 +3504,44 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1833300</v>
+        <v>1851900</v>
       </c>
       <c r="E46" s="3">
-        <v>1945000</v>
+        <v>1751500</v>
       </c>
       <c r="F46" s="3">
-        <v>1426400</v>
+        <v>1888700</v>
       </c>
       <c r="G46" s="3">
-        <v>1415900</v>
+        <v>1394900</v>
       </c>
       <c r="H46" s="3">
+        <v>1461000</v>
+      </c>
+      <c r="I46" s="3">
         <v>1533400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1712400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1590200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1351400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1439100</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3485,71 +3587,74 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>148700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>123000</v>
+      </c>
+      <c r="F47" s="3">
+        <v>97500</v>
+      </c>
+      <c r="G47" s="3">
+        <v>72800</v>
+      </c>
+      <c r="H47" s="3">
+        <v>49600</v>
+      </c>
+      <c r="I47" s="3">
+        <v>47200</v>
+      </c>
+      <c r="J47" s="3">
         <v>41300</v>
       </c>
-      <c r="E47" s="3">
-        <v>41300</v>
-      </c>
-      <c r="F47" s="3">
-        <v>41300</v>
-      </c>
-      <c r="G47" s="3">
-        <v>46400</v>
-      </c>
-      <c r="H47" s="3">
-        <v>47200</v>
-      </c>
-      <c r="I47" s="3">
-        <v>41300</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>51000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>41300</v>
       </c>
       <c r="L47" s="3">
         <v>41300</v>
       </c>
       <c r="M47" s="3">
+        <v>41300</v>
+      </c>
+      <c r="N47" s="3">
         <v>1094300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>782000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>704600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>673300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>319200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>192500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>110800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>82000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>104400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>151300</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3565,71 +3670,74 @@
       <c r="AB47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E48" s="3">
         <v>47800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>51500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>55200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>59100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>62800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>66000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>92900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>96700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>100500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>130500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>128500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>126400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>123000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>120400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>88900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>29800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>27400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>28300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>23000</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3645,62 +3753,65 @@
       <c r="AB48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>113300</v>
+      </c>
+      <c r="E49" s="3">
         <v>111400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>107500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>106200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>106900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>107000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>109700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>111900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>97800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>111500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>82700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>83800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>84800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>85900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>87000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>87800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>89000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3716,8 +3827,8 @@
       <c r="Y49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,71 +4002,74 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>319800</v>
+      </c>
+      <c r="E52" s="3">
         <v>262500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>221700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>179900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>143700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>136600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>87700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>114600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>130600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>86400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>126800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>169500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>146400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>283700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>234600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>148200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>126200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>93300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>66500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>60500</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,71 +4168,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2477900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2296300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2367000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1809000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1820200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1927700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2017100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2001800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1763700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1821700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1936100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1915300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1917000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1987600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1820500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1606100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>904600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>488600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>477300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>309800</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4125,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,71 +4315,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E57" s="3">
         <v>13300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>109500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>104800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>127700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>150100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>114200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>93700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>94300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>64600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>59300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>45200</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4265,41 +4396,44 @@
       <c r="AB57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E58" s="3">
         <v>11600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>15400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11200</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>3800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11400</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4319,16 +4453,16 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>20500</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>16</v>
+      <c r="V58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>16</v>
@@ -4339,14 +4473,17 @@
       <c r="Z58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4377,39 +4514,39 @@
       <c r="L59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N59" s="3">
         <v>146100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>149200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>154700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>169800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>185900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>128700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>67000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>44700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>44200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>29900</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4425,41 +4562,44 @@
       <c r="AB59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>117700</v>
+      </c>
+      <c r="E60" s="3">
         <v>82100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>135900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>98600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>70500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>62500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>77200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>58400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>68200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>58000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -4505,71 +4645,74 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1529800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1446300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1524400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1037300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1075300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1182500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1244200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1246700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1009800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1088500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>986400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>918900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>856600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>769200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>695400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>649200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>21400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>62600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>100600</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4585,41 +4728,44 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>108400</v>
+      </c>
+      <c r="E62" s="3">
         <v>91200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>73500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>77600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>79800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>69900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>60500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>55900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>47600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>48000</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,71 +5060,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1755900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1619600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1733700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1213400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1225500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1314900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1381800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1361000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1125600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1194500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1263600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1196700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1159900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1111100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1013400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>887000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>188500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>168000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>177000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>194600</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4985,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5235,11 +5403,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>162500</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,71 +5506,74 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-408000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-413600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-411200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-408400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-401600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-347200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-282600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-240200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-199900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-171700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-42400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>69000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>98900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>66200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-21800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-59100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-69200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-70200</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5415,8 +5589,11 @@
       <c r="AB72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,71 +5838,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>722000</v>
+      </c>
+      <c r="E76" s="3">
         <v>676600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>633200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>595500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>594700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>612800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>635300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>640800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>638100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>627200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>672400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>718600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>757100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>876500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>807100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>719100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>716100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>320600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>300300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-47300</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5735,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-54500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-64600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-42400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-40300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-129300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-55300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-56200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-29900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>32700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>58900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>29100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>37300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>9700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,68 +6208,69 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E83" s="3">
         <v>5600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1700</v>
-      </c>
-      <c r="M83" s="3">
-        <v>3700</v>
       </c>
       <c r="N83" s="3">
         <v>3700</v>
       </c>
       <c r="O83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="P83" s="3">
         <v>3400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>600</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,68 +6704,71 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-120200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-110900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>179300</v>
       </c>
-      <c r="G89" s="3">
-        <v>65300</v>
-      </c>
       <c r="H89" s="3">
+        <v>73600</v>
+      </c>
+      <c r="I89" s="3">
         <v>44300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-145600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-107700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>217300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-75700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-252900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-101400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-53600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-266800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-11100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>43600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>92800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>43100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>68500</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6570,8 +6787,11 @@
       <c r="AB89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,68 +6820,69 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>16</v>
       </c>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,68 +7067,71 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-109800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-78600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-77900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-46200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-76100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-37500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-29900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-24200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-38500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-25900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-85100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-24200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>5200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-19800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-84400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-40600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>8800</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6920,8 +7150,11 @@
       <c r="AB94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6982,8 +7216,8 @@
       <c r="L96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,68 +7513,71 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>91900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-44700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>509300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-38000</v>
       </c>
-      <c r="G100" s="3">
-        <v>132300</v>
-      </c>
       <c r="H100" s="3">
+        <v>124000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-35400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>28300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>237100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-120800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>21000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>40500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>41100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-34700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>83100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>50400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>595000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>229300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-19300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>123400</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7350,8 +7596,11 @@
       <c r="AB100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7382,8 +7631,8 @@
       <c r="L101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7430,68 +7679,71 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-138100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-136700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>320500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>95100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>121500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-28600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-147200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>105100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>58000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-80600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-297500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-84500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-98300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-178500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>19500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>554200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>281500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>24700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>200700</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7508,6 +7760,9 @@
         <v>16</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>UPST</t>
   </si>
@@ -656,391 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>304200</v>
+      </c>
+      <c r="E8" s="3">
         <v>285900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>265100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>220400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>226400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>173000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>139100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>138500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>154400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>144000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>140000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>110100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>146900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>157200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>228200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>314000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>287400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>210400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>187300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>116200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>84400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>62900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>13300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>68000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>61100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>47900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>28600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E9" s="3">
         <v>49800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>46200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>40500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>40600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>39300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>38700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>39400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>36100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>36900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>36800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>40600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>43500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>45000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>51100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>48400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>41000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>35000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>24200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>17400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>252300</v>
+      </c>
+      <c r="E10" s="3">
         <v>236100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>218800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>179900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>185800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>133700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>100400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>99100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>118300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>107100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>103300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>69500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>103400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>112200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>177100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>265600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>246400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>175400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>163100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>98800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>71600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>53500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>59200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>52700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>41200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>23200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>66900</v>
+      </c>
+      <c r="E12" s="3">
         <v>64000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>68800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>57800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>67200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>64900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>58500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>63100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>57200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>54900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>58000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>110100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>64000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>66200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>57000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>50000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>46500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>37100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>31400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>19000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>14200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>7300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>5100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1243,29 +1259,32 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>-7200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-33400</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1281,8 +1300,8 @@
       <c r="N14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1329,47 +1348,50 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E15" s="3">
         <v>6100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6400</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1415,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>277200</v>
+      </c>
+      <c r="E17" s="3">
         <v>253400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>252700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>217900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>223700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>207300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>183100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>195300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>187800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>178400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>169100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>234800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>205400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>215300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>260300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>279100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>227000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>181800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>151000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>100600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>74000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>53200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>28700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>63400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>59100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>47500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>34100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E18" s="3">
         <v>32500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-34300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-44000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-56800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-33400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-34400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-29100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-124700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-58500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-58100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-32100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>34900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>60400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>28600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>36300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>15600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-15400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1648,219 +1680,226 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>13500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-700</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-5300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-9000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>9300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E21" s="3">
         <v>39600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-23900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-38200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-48200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-37300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-18600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-114900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-52100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-52500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-26500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>35500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>61800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>30000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>38300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB21" s="3">
         <v>5700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>100</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E22" s="3">
         <v>8800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1906,112 +1945,118 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E23" s="3">
         <v>31900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-54500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-64600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-42300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-40300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-28100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-129200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-55700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-56200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-29800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>32700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>59300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>27800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>36300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>10300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -2019,11 +2064,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -2031,11 +2076,11 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-500</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -2043,23 +2088,23 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
@@ -2067,19 +2112,22 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
         <v>0</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E26" s="3">
         <v>31800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-54500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-64600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-42400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-40300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-129300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-55300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-56200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-29900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>32700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>58900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>29100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>37300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>10100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>9700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E27" s="3">
         <v>31800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-54500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-64600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-42400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-40300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-28200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-129300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-55300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-56200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-29900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>32700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>58900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>29100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>37300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>10100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>9700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E32" s="3">
         <v>1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-13500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>700</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>5300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>9000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E33" s="3">
         <v>31800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-54500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-64600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-42400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-40300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-129300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-55300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-56200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-29900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>32700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>58900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>29100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>37300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>10100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>9700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E35" s="3">
         <v>31800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-54500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-64600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-42400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-40300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-129300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-55300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-56200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-29900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>32700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>58900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>29100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>37300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>10100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>9700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,77 +3264,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>652400</v>
+      </c>
+      <c r="E41" s="3">
         <v>489800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>395900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>599800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>788400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>445300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>374800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>300500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>368400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>516600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>443700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>386900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>422400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>684000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>790400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>757800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>986600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1041500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>506300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>257000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>250800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>53200</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3265,38 +3351,41 @@
       <c r="AD41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E42" s="3">
         <v>5900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>14900</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3351,77 +3440,80 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1128600</v>
+      </c>
+      <c r="E43" s="3">
         <v>1350300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1118900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>877200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>876600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>712500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>872300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1094200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1211800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>975100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>841500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>987200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>46700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>49900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>46100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>48600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>55500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>30000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>31700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>18100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9100</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3437,8 +3529,11 @@
       <c r="AD43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3475,8 +3570,8 @@
       <c r="N44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3523,8 +3618,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3561,8 +3659,8 @@
       <c r="N45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -3609,47 +3707,50 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2230600</v>
+      </c>
+      <c r="E46" s="3">
         <v>2223600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1851900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1751500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1888700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1394900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1461000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1533400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1712400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1590200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1351400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1439100</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3695,77 +3796,80 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E47" s="3">
         <v>156100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>148700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>123000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>97500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>72800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>49600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>47200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>41300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>51000</v>
-      </c>
-      <c r="M47" s="3">
-        <v>41300</v>
       </c>
       <c r="N47" s="3">
         <v>41300</v>
       </c>
       <c r="O47" s="3">
+        <v>41300</v>
+      </c>
+      <c r="P47" s="3">
         <v>1094300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>782000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>704600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>673300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>319200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>192500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>110800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>82000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>104400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>151300</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3781,77 +3885,80 @@
       <c r="AD47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E48" s="3">
         <v>40500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>44200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>47800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>51500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>55200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>59100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>62800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>66000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>92900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>96700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>100500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>130500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>128500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>126400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>123000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>120400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>88900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>29800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>27400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>28300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>23000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3867,68 +3974,71 @@
       <c r="AD48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>113900</v>
+      </c>
+      <c r="E49" s="3">
         <v>114000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>113300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>111400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>107500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>106200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>106900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>107000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>109700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>111900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>97800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>111500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>82700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>83800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>84800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>85900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>87000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>87800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>89000</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3944,8 +4054,8 @@
       <c r="AA49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
+      <c r="AB49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
@@ -3953,8 +4063,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,77 +4241,80 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>454300</v>
+      </c>
+      <c r="E52" s="3">
         <v>370600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>319800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>262500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>221700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>179900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>143700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>136600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>87700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>114600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>130600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>86400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>126800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>169500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>146400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>283700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>234600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>148200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>126200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>93300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>66500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>60500</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4211,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,77 +4419,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2974800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2904800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2477900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2296300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2367000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1809000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1820200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1927700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2017100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2001800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1763700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1821700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1936100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1915300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1917000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1987600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1820500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1606100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>904600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>488600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>477300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>309800</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4383,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,77 +4576,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E57" s="3">
         <v>11800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>109500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>104800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>127700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>150100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>114200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>93700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>94300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>64600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>59300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>45200</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4533,47 +4663,50 @@
       <c r="AD57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E58" s="3">
         <v>3900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11600</v>
       </c>
-      <c r="G58" s="3">
-        <v>15400</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>3800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>3800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>17100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11400</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4593,16 +4726,16 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>20500</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3" t="s">
-        <v>16</v>
+      <c r="X58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>16</v>
@@ -4613,14 +4746,17 @@
       <c r="AB58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4657,39 +4793,39 @@
       <c r="N59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P59" s="3">
         <v>146100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>149200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>154700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>169800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>185900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>128700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>67000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>44700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>44200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>29900</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4705,47 +4841,50 @@
       <c r="AD59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>170200</v>
+      </c>
+      <c r="E60" s="3">
         <v>99800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>117700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>82100</v>
       </c>
-      <c r="G60" s="3">
-        <v>135900</v>
-      </c>
       <c r="H60" s="3">
+        <v>120500</v>
+      </c>
+      <c r="I60" s="3">
         <v>98600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>70500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>62500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>77200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>58400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>68200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>58000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -4791,77 +4930,80 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1886200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1947600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1529800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1446300</v>
       </c>
-      <c r="G61" s="3">
-        <v>1524400</v>
-      </c>
       <c r="H61" s="3">
+        <v>1539800</v>
+      </c>
+      <c r="I61" s="3">
         <v>1037300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1075300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1182500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1244200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1246700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1009800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1088500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>986400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>918900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>856600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>769200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>695400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>649200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>21400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>62600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>100600</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4877,47 +5019,50 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>119500</v>
+      </c>
+      <c r="E62" s="3">
         <v>113700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>108400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>91200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>73500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>77600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>79800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>69900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>60500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>55900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>47600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>48000</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -4963,8 +5108,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,77 +5375,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2176000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2161100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1755900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1619600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1733700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1213400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1225500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1314900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1381800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1361000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1125600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1194500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1263600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1196700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1159900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1111100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1013400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>887000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>188500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>168000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>177000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>194600</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5307,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5577,11 +5744,11 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>162500</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5597,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,77 +5853,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-357600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-376200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-408000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-413600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-411200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-408400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-401600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-347200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-282600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-240200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-199900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-171700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-42400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>69000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>98900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>66200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-21800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-59100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-69200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-70200</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5769,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,77 +6209,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>798800</v>
+      </c>
+      <c r="E76" s="3">
         <v>743700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>722000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>676600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>633200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>595500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>594700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>612800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>635300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>640800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>638100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>627200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>672400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>718600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>757100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>876500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>807100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>719100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>716100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>320600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>300300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-47300</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6113,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E81" s="3">
         <v>31800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-54500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-64600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-42400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-40300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-129300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-55300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-56200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-29900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>32700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>58900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>29100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>37300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>10100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>9700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,74 +6605,75 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E83" s="3">
         <v>5400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1700</v>
-      </c>
-      <c r="O83" s="3">
-        <v>3700</v>
       </c>
       <c r="P83" s="3">
         <v>3700</v>
       </c>
       <c r="Q83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="R83" s="3">
         <v>3400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>600</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6494,8 +6692,11 @@
       <c r="AD83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,74 +7137,77 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>108600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-122600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-120200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-110900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>179300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>73600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>44300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-145600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-107700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>217300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-75700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-252900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-101400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-53600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-266800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-11100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>43600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>92800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>43100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>68500</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>16</v>
       </c>
@@ -7010,8 +7226,11 @@
       <c r="AD89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,74 +7261,75 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>16</v>
       </c>
@@ -7128,8 +7348,11 @@
       <c r="AD91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,74 +7526,77 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>131700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-120500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-109800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-78600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-77900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-46200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-76100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-37500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-29900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-24200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-38500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-25900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-85100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>5200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-19800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-84400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-40600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>8800</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7386,8 +7615,11 @@
       <c r="AD94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7456,8 +7689,8 @@
       <c r="N96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7504,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,74 +8004,77 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E100" s="3">
         <v>378600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>91900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-44700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>509300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-38000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>124000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-35400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>28300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>237100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-120800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>21000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>40500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>41100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-34700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>83100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>50400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>595000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>229300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-19300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>123400</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7848,8 +8093,11 @@
       <c r="AD100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7886,8 +8134,8 @@
       <c r="N101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7934,74 +8182,77 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>220100</v>
+      </c>
+      <c r="E102" s="3">
         <v>135400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-138100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-136700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>320500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>95100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>121500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-28600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-147200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>105100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>58000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-80600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-297500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-84500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-98300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-178500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>19500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>554200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>281500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>24700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>200700</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>16</v>
       </c>
@@ -8018,6 +8269,9 @@
         <v>16</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>UPST</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>318600</v>
+      </c>
+      <c r="E8" s="3">
         <v>304200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>285900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>265100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>220400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>226400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>173000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>139100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>138500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>154400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>144000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>140000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>110100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>146900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>157200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>228200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>314000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>287400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>210400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>187300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>116200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>84400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>62900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>13300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>68000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>61100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>47900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>28600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>55100</v>
+      </c>
+      <c r="E9" s="3">
         <v>51800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>49800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>46200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>40500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>40600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>39300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>38700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>39400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>36100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>36900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>36800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>40600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>43500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>45000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>51100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>48400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>41000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>35000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>24200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>17400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>263500</v>
+      </c>
+      <c r="E10" s="3">
         <v>252300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>236100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>218800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>179900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>185800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>133700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>100400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>99100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>118300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>107100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>103300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>69500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>103400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>112200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>177100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>265600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>246400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>175400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>163100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>98800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>71600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>53500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>59200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>52700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>41200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>23200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E12" s="3">
         <v>66900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>64000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>68800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>57800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>67200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>64900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>58500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>63100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>57200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>54900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>58000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>110100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>64000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>66200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>57000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>50000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>46500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>37100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>31400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>19000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>14200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>7000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>5100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1262,32 +1279,35 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-7200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-33400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1303,8 +1323,8 @@
       <c r="O14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1351,50 +1371,53 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E15" s="3">
         <v>6500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6400</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>315700</v>
+      </c>
+      <c r="E17" s="3">
         <v>277200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>253400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>252700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>217900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>223700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>207300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>183100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>195300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>187800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>178400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>169100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>234800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>205400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>215300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>260300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>279100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>227000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>181800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>151000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>100600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>74000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>53200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>28700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>63400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>59100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>47500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>34100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E18" s="3">
         <v>27000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>32500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-34300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-44000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-56800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-33400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-34400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-29100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-124700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-58500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-58100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-32100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>34900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>60400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>28600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>36300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>15600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-15400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1681,228 +1714,235 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>24100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>13500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-700</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-5300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>9300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E21" s="3">
         <v>9400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>39600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-23900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-38200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-48200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-37300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-26000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-18600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-114900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-52100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-52500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-26500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>35500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>61800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>30000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>38300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>11100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC21" s="3">
         <v>5700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>100</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E22" s="3">
         <v>8100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7100</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1948,118 +1988,124 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E23" s="3">
         <v>19200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>31900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-54500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-64600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-42300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-40300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-129200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-55700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-56200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-29800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>32700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>59300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>27800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>36300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>10300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>9700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -2067,11 +2113,11 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -2079,11 +2125,11 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-500</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -2091,23 +2137,23 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
@@ -2115,19 +2161,22 @@
         <v>0</v>
       </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E26" s="3">
         <v>18600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>31800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-54500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-64600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-42400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-40300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-28200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-129300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-55300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-56200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-29900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>32700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>58900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>29100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>37300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>10100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>9700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E27" s="3">
         <v>18600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>31800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-54500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-64600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-42400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-40300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-28200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-129300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-55300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-56200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-29900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>32700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>58900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>29100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>37300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>10100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>9700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-24100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-13500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>700</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>5300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>9000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E33" s="3">
         <v>18600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>31800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-54500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-64600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-42400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-40300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-28200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-129300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-55300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-56200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-29900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>32700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>58900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>29100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>37300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>10100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>9700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E35" s="3">
         <v>18600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>31800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-54500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-64600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-42400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-40300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-28200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-129300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-55300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-56200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-29900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>32700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>58900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>29100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>37300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>10100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>9700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,80 +3351,81 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>472900</v>
+      </c>
+      <c r="E41" s="3">
         <v>652400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>489800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>395900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>599800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>788400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>445300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>374800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>300500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>368400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>516600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>443700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>386900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>422400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>684000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>790400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>757800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>986600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1041500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>506300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>257000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>250800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>53200</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3354,41 +3441,44 @@
       <c r="AE41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E42" s="3">
         <v>5300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>14900</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -3443,80 +3533,83 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1165200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1128600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1350300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1118900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>877200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>876600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>712500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>872300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1094200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1211800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>975100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>841500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>987200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>46700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>49900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>46100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>48600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>55500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>30000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>31700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>18100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>11700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>9100</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3532,8 +3625,11 @@
       <c r="AE43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3573,8 +3669,8 @@
       <c r="O44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3662,8 +3761,8 @@
       <c r="O45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
+      <c r="P45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
@@ -3710,50 +3809,53 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2138900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2230600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2223600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1851900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1751500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1888700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1394900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1461000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1533400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1712400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1590200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1351400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1439100</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3799,80 +3901,83 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>153200</v>
+      </c>
+      <c r="E47" s="3">
         <v>154000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>156100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>148700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>123000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>97500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>72800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>49600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>47200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>41300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>51000</v>
-      </c>
-      <c r="N47" s="3">
-        <v>41300</v>
       </c>
       <c r="O47" s="3">
         <v>41300</v>
       </c>
       <c r="P47" s="3">
+        <v>41300</v>
+      </c>
+      <c r="Q47" s="3">
         <v>1094300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>782000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>704600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>673300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>319200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>192500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>110800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>82000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>104400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>151300</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3888,80 +3993,83 @@
       <c r="AE47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E48" s="3">
         <v>22100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>44200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>47800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>51500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>55200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>59100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>62800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>66000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>92900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>96700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>100500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>130500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>128500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>126400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>123000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>120400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>88900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>29800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>27400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>28300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>23000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3977,71 +4085,74 @@
       <c r="AE48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>115300</v>
+      </c>
+      <c r="E49" s="3">
         <v>113900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>114000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>113300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>111400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>107500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>106200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>106900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>107000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>109700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>111900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>97800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>111500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>82700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>83800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>84800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>85900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>87000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>87800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>89000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4057,8 +4168,8 @@
       <c r="AB49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,80 +4361,83 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>533000</v>
+      </c>
+      <c r="E52" s="3">
         <v>454300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>370600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>319800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>262500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>221700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>179900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>143700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>136600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>87700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>114600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>130600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>86400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>126800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>169500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>146400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>283700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>234600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>148200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>126200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>93300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>66500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>60500</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,80 +4545,83 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2961700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2974800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2904800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2477900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2296300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2367000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1809000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1820200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1927700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2017100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2001800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1763700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1821700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1936100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1915300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1917000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1987600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1820500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1606100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>904600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>488600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>477300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>309800</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,80 +4707,81 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E57" s="3">
         <v>32000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>109500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>104800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>127700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>150100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>114200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>93700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>94300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>64600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>59300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>45200</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4666,50 +4797,53 @@
       <c r="AE57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E58" s="3">
         <v>10600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11600</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>3800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>3800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>17100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11400</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4729,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>20500</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>16</v>
+      <c r="Y58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>16</v>
@@ -4749,14 +4883,17 @@
       <c r="AC58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4796,39 +4933,39 @@
       <c r="O59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q59" s="3">
         <v>146100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>149200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>154700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>169800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>185900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>128700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>67000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>44700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>44200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>29900</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4844,50 +4981,53 @@
       <c r="AE59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>183600</v>
+      </c>
+      <c r="E60" s="3">
         <v>170200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>99800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>117700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>82100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>120500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>98600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>70500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>62500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>77200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>58400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>68200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>58000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -4933,80 +5073,83 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1905200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1886200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1947600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1529800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1446300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1539800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1037300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1075300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1182500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1244200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1246700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1009800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1088500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>986400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>918900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>856600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>769200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>695400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>649200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>21400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>62600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>100600</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5022,50 +5165,53 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>139700</v>
+      </c>
+      <c r="E62" s="3">
         <v>119500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>113700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>108400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>91200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>73500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>77600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>79800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>69900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>60500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>55900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>47600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>48000</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,80 +5533,83 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2228500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2176000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2161100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1755900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1619600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1733700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1213400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1225500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1314900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1381800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1361000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1125600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1194500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1263600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1196700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1159900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1111100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1013400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>887000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>188500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>168000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>177000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>194600</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5747,11 +5915,11 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>162500</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,80 +6027,83 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-364200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-357600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-376200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-408000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-413600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-411200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-408400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-401600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-347200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-282600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-240200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-199900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-171700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-42400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>69000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>98900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>66200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-21800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-59100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-69200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-70200</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,80 +6395,83 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>733200</v>
+      </c>
+      <c r="E76" s="3">
         <v>798800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>743700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>722000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>676600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>633200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>595500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>594700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>612800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>635300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>640800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>638100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>627200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>672400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>718600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>757100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>876500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>807100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>719100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>716100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>320600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>300300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-47300</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E81" s="3">
         <v>18600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>31800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-54500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-64600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-42400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-40300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-28200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-129300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-55300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-56200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-29900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>32700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>58900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>29100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>37300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>10100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>9700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,77 +6804,78 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E83" s="3">
         <v>4700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1700</v>
-      </c>
-      <c r="P83" s="3">
-        <v>3700</v>
       </c>
       <c r="Q83" s="3">
         <v>3700</v>
       </c>
       <c r="R83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="S83" s="3">
         <v>3400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>600</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,77 +7354,80 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-133300</v>
+      </c>
+      <c r="E89" s="3">
         <v>108600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-122600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-120200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-110900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>179300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>73600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>44300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-145600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-107700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>217300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-75700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-252900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-101400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-53600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-266800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-11100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>43600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>92800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>43100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>68500</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>16</v>
       </c>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,77 +7482,78 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>16</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,77 +7756,80 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>900</v>
+      </c>
+      <c r="E94" s="3">
         <v>131700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-120500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-109800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-78600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-77900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-46200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-76100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-37500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-29900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-24200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-38500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-25900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-85100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-24200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>5200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-84400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-40600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>8800</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7692,8 +7926,8 @@
       <c r="O96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,77 +8250,80 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>378600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>91900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-44700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>509300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-38000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>124000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-35400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>28300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>237100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-120800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>21000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>40500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>41100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-34700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>83100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>50400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>595000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>229300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-19300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>123400</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>16</v>
       </c>
@@ -8096,8 +8342,11 @@
       <c r="AE100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8137,8 +8386,8 @@
       <c r="O101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8185,77 +8434,80 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-125700</v>
+      </c>
+      <c r="E102" s="3">
         <v>220100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>135400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-138100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-136700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>320500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>95100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>121500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-147200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>105100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>58000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-80600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-297500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-84500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-98300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-178500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>19500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>554200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>281500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>24700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>200700</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>16</v>
       </c>
@@ -8272,6 +8524,9 @@
         <v>16</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>16</v>
       </c>
     </row>
